--- a/SOT_results/SOT_all_angles_52point.xlsx
+++ b/SOT_results/SOT_all_angles_52point.xlsx
@@ -459,7 +459,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>16.90153589494063</v>
+        <v>17.47943486872997</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>16.88230956040268</v>
+        <v>17.10272421664234</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>16.88094840397522</v>
+        <v>16.80418393457441</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>16.88060811486835</v>
+        <v>16.83684697057579</v>
       </c>
     </row>
     <row r="6">
@@ -491,7 +491,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>16.88111854852865</v>
+        <v>16.89469536107498</v>
       </c>
     </row>
     <row r="7">
@@ -499,7 +499,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88026782576149</v>
+        <v>16.89952936182164</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>16.87992753665462</v>
+        <v>16.87219303771848</v>
       </c>
     </row>
     <row r="9">
@@ -515,7 +515,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>16.88196927129582</v>
+        <v>16.87124308618445</v>
       </c>
     </row>
     <row r="10">
@@ -523,7 +523,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>16.88026782576149</v>
+        <v>16.87043280080362</v>
       </c>
     </row>
     <row r="11">
@@ -531,7 +531,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>16.88435129504388</v>
+        <v>16.86388013044959</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +539,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>16.88281999406298</v>
+        <v>16.85969901354604</v>
       </c>
     </row>
     <row r="13">
@@ -547,7 +547,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>16.88111854852865</v>
+        <v>16.86149527546073</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>16.88213941584925</v>
+        <v>16.86003709431369</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>16.88179912674238</v>
+        <v>16.85898959816473</v>
       </c>
     </row>
     <row r="16">
@@ -571,7 +571,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>16.88401100593702</v>
+        <v>16.85777638701655</v>
       </c>
     </row>
     <row r="17">
@@ -579,7 +579,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>16.88537216236448</v>
+        <v>17.04785370805233</v>
       </c>
     </row>
     <row r="18">
@@ -587,7 +587,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>16.88401100593702</v>
+        <v>17.37541074190787</v>
       </c>
     </row>
     <row r="19">
@@ -595,7 +595,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>16.88520201781105</v>
+        <v>17.57173479791449</v>
       </c>
     </row>
     <row r="20">
@@ -603,7 +603,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>16.88605274057822</v>
+        <v>17.58320127824558</v>
       </c>
     </row>
     <row r="21">
@@ -611,7 +611,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>16.88486172870418</v>
+        <v>17.57560166597336</v>
       </c>
     </row>
     <row r="22">
@@ -619,7 +619,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>16.88622288513165</v>
+        <v>17.5380569653794</v>
       </c>
     </row>
     <row r="23">
@@ -627,7 +627,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>16.88707360789881</v>
+        <v>17.48530971485639</v>
       </c>
     </row>
     <row r="24">
@@ -635,7 +635,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>16.89047649896747</v>
+        <v>17.10180253087741</v>
       </c>
     </row>
     <row r="25">
@@ -643,7 +643,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>16.90561936422302</v>
+        <v>17.3916253172168</v>
       </c>
     </row>
     <row r="26">
@@ -651,7 +651,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>16.96925342720702</v>
+        <v>17.59302945243047</v>
       </c>
     </row>
     <row r="27">
@@ -659,7 +659,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>17.04173500696954</v>
+        <v>17.40216013562916</v>
       </c>
     </row>
     <row r="28">
@@ -667,7 +667,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>17.01400144475994</v>
+        <v>17.40497230253911</v>
       </c>
     </row>
     <row r="29">
@@ -675,7 +675,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>17.02744286448116</v>
+        <v>17.4892259094535</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>17.03135618921012</v>
+        <v>17.41097185058803</v>
       </c>
     </row>
     <row r="31">
@@ -691,7 +691,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>17.04037385054207</v>
+        <v>17.64260871989134</v>
       </c>
     </row>
     <row r="32">
@@ -699,7 +699,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>17.03969327232834</v>
+        <v>17.65801744366556</v>
       </c>
     </row>
     <row r="33">
@@ -707,7 +707,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>17.04037385054207</v>
+        <v>17.54056596805999</v>
       </c>
     </row>
     <row r="34">
@@ -715,7 +715,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>17.04394688616417</v>
+        <v>17.1117071889081</v>
       </c>
     </row>
     <row r="35">
@@ -723,7 +723,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>17.0425857297367</v>
+        <v>17.04424400306918</v>
       </c>
     </row>
     <row r="36">
@@ -731,7 +731,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>17.04496775348477</v>
+        <v>17.04272984461471</v>
       </c>
     </row>
     <row r="37">
@@ -739,7 +739,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>17.0482005</v>
+        <v>17.03027627928823</v>
       </c>
     </row>
     <row r="38">
@@ -747,7 +747,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>17.0446274643779</v>
+        <v>17.02803275314485</v>
       </c>
     </row>
     <row r="39">
@@ -755,7 +755,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>17.04700948812597</v>
+        <v>17.02596713507758</v>
       </c>
     </row>
     <row r="40">
@@ -763,7 +763,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>17.0482005</v>
+        <v>17.02817740737495</v>
       </c>
     </row>
     <row r="41">
@@ -771,7 +771,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>17.05568686035106</v>
+        <v>17.02613672969217</v>
       </c>
     </row>
     <row r="42">
@@ -779,7 +779,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>17.0482005</v>
+        <v>17.02222275201813</v>
       </c>
     </row>
     <row r="43">
@@ -787,7 +787,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>17.0492213673206</v>
+        <v>17.02068864125606</v>
       </c>
     </row>
     <row r="44">
@@ -795,7 +795,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>17.04956165642746</v>
+        <v>17.01449067859268</v>
       </c>
     </row>
     <row r="45">
@@ -803,7 +803,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>17.0492213673206</v>
+        <v>17.07331340677963</v>
       </c>
     </row>
     <row r="46">
@@ -811,7 +811,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>17.04956165642746</v>
+        <v>17.18785129124496</v>
       </c>
     </row>
     <row r="47">
@@ -819,7 +819,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>17.0487109336603</v>
+        <v>17.27457399622474</v>
       </c>
     </row>
     <row r="48">
@@ -827,7 +827,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>17.04837064455343</v>
+        <v>17.32125685369913</v>
       </c>
     </row>
     <row r="49">
@@ -835,7 +835,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>17.04939151187403</v>
+        <v>17.11974187233213</v>
       </c>
     </row>
     <row r="50">
@@ -843,7 +843,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>17.04598862080537</v>
+        <v>17.10853976007673</v>
       </c>
     </row>
     <row r="51">
@@ -851,7 +851,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>17.02897416546205</v>
+        <v>17.12700506652899</v>
       </c>
     </row>
     <row r="52">
@@ -859,7 +859,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>16.93896769669592</v>
+        <v>17.36856543770906</v>
       </c>
     </row>
     <row r="53">
@@ -867,7 +867,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>16.8448777586474</v>
+        <v>17.44820618195268</v>
       </c>
     </row>
   </sheetData>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.164785（按前次分析的平台差模型）</t>
+          <t>0.164785（保持前次角度模型）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.5263596444（按前次分析的平台差模型）</t>
+          <t>0.5263596444（保持前次角度模型）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.7653084889（按前次分析的平台差模型）</t>
+          <t>0.7653084889（保持前次角度模型）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.851626（按前次分析的平台差模型）</t>
+          <t>0.851626（保持前次角度模型）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.8122403338（按前次分析的平台差模型）</t>
+          <t>0.8122403338（保持前次角度模型）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2546,7 +2546,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>11.98368188139051</v>
+        <v>13.17773356095276</v>
       </c>
     </row>
     <row r="3">
@@ -2554,7 +2554,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>11.92226872721165</v>
+        <v>12.37553560654939</v>
       </c>
     </row>
     <row r="4">
@@ -2562,7 +2562,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>11.91792089328749</v>
+        <v>11.73979992385841</v>
       </c>
     </row>
     <row r="5">
@@ -2570,7 +2570,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>11.91683393480644</v>
+        <v>11.80976015985502</v>
       </c>
     </row>
     <row r="6">
@@ -2578,7 +2578,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>11.91846437252801</v>
+        <v>11.93571315045511</v>
       </c>
     </row>
     <row r="7">
@@ -2586,7 +2586,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>11.91574697632541</v>
+        <v>11.9478811276776</v>
       </c>
     </row>
     <row r="8">
@@ -2594,7 +2594,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>11.91466001784436</v>
+        <v>11.88920660377777</v>
       </c>
     </row>
     <row r="9">
@@ -2602,7 +2602,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>11.92118176873062</v>
+        <v>11.88732083484917</v>
       </c>
     </row>
     <row r="10">
@@ -2610,7 +2610,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>11.91574697632541</v>
+        <v>11.88537602118982</v>
       </c>
     </row>
     <row r="11">
@@ -2618,7 +2618,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>11.92879047809791</v>
+        <v>11.87171128689949</v>
       </c>
     </row>
     <row r="12">
@@ -2626,7 +2626,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>11.92389916493321</v>
+        <v>11.8631872675331</v>
       </c>
     </row>
     <row r="13">
@@ -2634,7 +2634,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>11.91846437252801</v>
+        <v>11.86729511009491</v>
       </c>
     </row>
     <row r="14">
@@ -2642,7 +2642,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>11.92172524797114</v>
+        <v>11.86399387869406</v>
       </c>
     </row>
     <row r="15">
@@ -2650,7 +2650,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>11.92063828949009</v>
+        <v>11.86162158468165</v>
       </c>
     </row>
     <row r="16">
@@ -2658,7 +2658,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>11.92770351961686</v>
+        <v>11.85911265082287</v>
       </c>
     </row>
     <row r="17">
@@ -2666,7 +2666,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>11.93205135354103</v>
+        <v>12.26374055467733</v>
       </c>
     </row>
     <row r="18">
@@ -2674,7 +2674,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>11.92770351961686</v>
+        <v>12.96107597587945</v>
       </c>
     </row>
     <row r="19">
@@ -2682,7 +2682,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>11.93150787430051</v>
+        <v>13.37847210660041</v>
       </c>
     </row>
     <row r="20">
@@ -2690,7 +2690,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>11.93422527050312</v>
+        <v>13.40105990187159</v>
       </c>
     </row>
     <row r="21">
@@ -2698,7 +2698,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>11.93042091581947</v>
+        <v>13.38265288510657</v>
       </c>
     </row>
     <row r="22">
@@ -2706,7 +2706,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>11.93476874974364</v>
+        <v>13.30040617868298</v>
       </c>
     </row>
     <row r="23">
@@ -2714,7 +2714,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>11.93748614594624</v>
+        <v>13.16662217718366</v>
       </c>
     </row>
     <row r="24">
@@ -2722,7 +2722,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>11.94835573075665</v>
+        <v>12.36418399676562</v>
       </c>
     </row>
     <row r="25">
@@ -2730,7 +2730,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>11.99672538316301</v>
+        <v>12.96136472751776</v>
       </c>
     </row>
     <row r="26">
@@ -2738,7 +2738,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>12.19998661911781</v>
+        <v>13.3846467114349</v>
       </c>
     </row>
     <row r="27">
@@ -2746,7 +2746,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>12.43150877557969</v>
+        <v>12.97819424016057</v>
       </c>
     </row>
     <row r="28">
@@ -2754,7 +2754,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>12.34292165937479</v>
+        <v>13.33508912410903</v>
       </c>
     </row>
     <row r="29">
@@ -2762,7 +2762,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>12.38585651937594</v>
+        <v>13.51450552962682</v>
       </c>
     </row>
     <row r="30">
@@ -2770,7 +2770,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>12.39835654190791</v>
+        <v>13.3228734192533</v>
       </c>
     </row>
     <row r="31">
@@ -2778,7 +2778,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>12.42716094165552</v>
+        <v>13.71701415982138</v>
       </c>
     </row>
     <row r="32">
@@ -2786,7 +2786,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>12.42498702469343</v>
+        <v>13.75444519258381</v>
       </c>
     </row>
     <row r="33">
@@ -2794,7 +2794,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>12.42716094165552</v>
+        <v>13.49245611516705</v>
       </c>
     </row>
     <row r="34">
@@ -2802,7 +2802,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>12.43857400570645</v>
+        <v>12.57758148608428</v>
       </c>
     </row>
     <row r="35">
@@ -2810,7 +2810,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>12.43422617178228</v>
+        <v>12.43138673690372</v>
       </c>
     </row>
     <row r="36">
@@ -2818,7 +2818,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>12.44183488114958</v>
+        <v>12.42793374488073</v>
       </c>
     </row>
     <row r="37">
@@ -2826,7 +2826,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>12.45216098671948</v>
+        <v>12.4015762104699</v>
       </c>
     </row>
     <row r="38">
@@ -2834,7 +2834,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>12.44074792266854</v>
+        <v>12.39686177420067</v>
       </c>
     </row>
     <row r="39">
@@ -2842,7 +2842,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>12.44835663203583</v>
+        <v>12.3925818051007</v>
       </c>
     </row>
     <row r="40">
@@ -2850,7 +2850,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>12.45216098671948</v>
+        <v>12.39722479549429</v>
       </c>
     </row>
     <row r="41">
@@ -2858,7 +2858,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>12.4760740733024</v>
+        <v>12.39270635773545</v>
       </c>
     </row>
     <row r="42">
@@ -2866,7 +2866,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>12.45216098671948</v>
+        <v>12.38430999515282</v>
       </c>
     </row>
     <row r="43">
@@ -2874,7 +2874,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>12.4554218621626</v>
+        <v>12.38107977788297</v>
       </c>
     </row>
     <row r="44">
@@ -2882,7 +2882,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>12.45650882064364</v>
+        <v>12.36793737943099</v>
       </c>
     </row>
     <row r="45">
@@ -2890,7 +2890,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>12.4554218621626</v>
+        <v>12.49304017641562</v>
       </c>
     </row>
     <row r="46">
@@ -2898,7 +2898,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>12.45650882064364</v>
+        <v>12.73622306873994</v>
       </c>
     </row>
     <row r="47">
@@ -2906,7 +2906,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>12.45379142444104</v>
+        <v>12.91827225430441</v>
       </c>
     </row>
     <row r="48">
@@ -2914,7 +2914,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>12.45270446595999</v>
+        <v>13.00983049693937</v>
       </c>
     </row>
     <row r="49">
@@ -2922,7 +2922,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>12.45596534140313</v>
+        <v>12.61395046535296</v>
       </c>
     </row>
     <row r="50">
@@ -2930,7 +2930,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>12.44509575659271</v>
+        <v>12.52393337593741</v>
       </c>
     </row>
     <row r="51">
@@ -2938,7 +2938,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>12.39074783254062</v>
+        <v>12.73306025493985</v>
       </c>
     </row>
     <row r="52">
@@ -2946,7 +2946,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>12.1032473143051</v>
+        <v>13.29254570896565</v>
       </c>
     </row>
     <row r="53">
@@ -2954,7 +2954,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>11.80270329429707</v>
+        <v>13.46213911378534</v>
       </c>
     </row>
   </sheetData>
@@ -2992,7 +2992,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>7.577975761335487</v>
+        <v>8.366266926306173</v>
       </c>
     </row>
     <row r="3">
@@ -3000,7 +3000,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>7.488683185966928</v>
+        <v>7.783083060659582</v>
       </c>
     </row>
     <row r="4">
@@ -3008,7 +3008,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>7.482361587710758</v>
+        <v>7.32091435164443</v>
       </c>
     </row>
     <row r="5">
@@ -3016,7 +3016,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>7.480781188146703</v>
+        <v>7.372657372439897</v>
       </c>
     </row>
     <row r="6">
@@ -3024,7 +3024,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>7.483151787492768</v>
+        <v>7.47025543984111</v>
       </c>
     </row>
     <row r="7">
@@ -3032,7 +3032,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>7.479200788582665</v>
+        <v>7.483188588592592</v>
       </c>
     </row>
     <row r="8">
@@ -3040,7 +3040,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>7.477620389018609</v>
+        <v>7.439524860393856</v>
       </c>
     </row>
     <row r="9">
@@ -3048,7 +3048,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>7.48710278640289</v>
+        <v>7.43845302201026</v>
       </c>
     </row>
     <row r="10">
@@ -3056,7 +3056,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>7.479200788582665</v>
+        <v>7.436560836277589</v>
       </c>
     </row>
     <row r="11">
@@ -3064,7 +3064,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>7.498165583351208</v>
+        <v>7.42725721413388</v>
       </c>
     </row>
     <row r="12">
@@ -3072,7 +3072,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>7.491053785312993</v>
+        <v>7.421888261011556</v>
       </c>
     </row>
     <row r="13">
@@ -3080,7 +3080,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>7.483151787492768</v>
+        <v>7.425491227348444</v>
       </c>
     </row>
     <row r="14">
@@ -3088,7 +3088,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>7.487892986184917</v>
+        <v>7.422663686362126</v>
       </c>
     </row>
     <row r="15">
@@ -3096,7 +3096,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>7.486312586620862</v>
+        <v>7.420630092095929</v>
       </c>
     </row>
     <row r="16">
@@ -3104,7 +3104,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>7.496585183787153</v>
+        <v>7.418968786397502</v>
       </c>
     </row>
     <row r="17">
@@ -3112,7 +3112,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>7.50290678204334</v>
+        <v>7.712825155392096</v>
       </c>
     </row>
     <row r="18">
@@ -3120,7 +3120,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>7.496585183787153</v>
+        <v>8.219359526865805</v>
       </c>
     </row>
     <row r="19">
@@ -3128,7 +3128,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>7.502116582261312</v>
+        <v>8.521333388293762</v>
       </c>
     </row>
     <row r="20">
@@ -3136,7 +3136,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>7.506067581171433</v>
+        <v>8.533763513239384</v>
       </c>
     </row>
     <row r="21">
@@ -3144,7 +3144,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500536182697275</v>
+        <v>8.515531962378061</v>
       </c>
     </row>
     <row r="22">
@@ -3152,7 +3152,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>7.506857780953461</v>
+        <v>8.450732587372531</v>
       </c>
     </row>
     <row r="23">
@@ -3160,7 +3160,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>7.510808779863565</v>
+        <v>8.306671341373042</v>
       </c>
     </row>
     <row r="24">
@@ -3168,7 +3168,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>7.526612775504015</v>
+        <v>7.754353945805643</v>
       </c>
     </row>
     <row r="25">
@@ -3176,7 +3176,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>7.59694055610403</v>
+        <v>8.144894088974961</v>
       </c>
     </row>
     <row r="26">
@@ -3184,7 +3184,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>7.892475274580483</v>
+        <v>8.44039026402805</v>
       </c>
     </row>
     <row r="27">
@@ -3192,7 +3192,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>8.2291003817221</v>
+        <v>8.144906434758418</v>
       </c>
     </row>
     <row r="28">
@@ -3200,7 +3200,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>8.100297817252418</v>
+        <v>9.169671254739878</v>
       </c>
     </row>
     <row r="29">
@@ -3208,7 +3208,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>8.162723600032207</v>
+        <v>9.300103839809365</v>
       </c>
     </row>
     <row r="30">
@@ -3216,7 +3216,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>8.180898195018722</v>
+        <v>9.106285230180562</v>
       </c>
     </row>
     <row r="31">
@@ -3224,7 +3224,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>8.222778783465914</v>
+        <v>9.176631280010083</v>
       </c>
     </row>
     <row r="32">
@@ -3232,7 +3232,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>8.21961798433782</v>
+        <v>9.213915598172079</v>
       </c>
     </row>
     <row r="33">
@@ -3240,7 +3240,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>8.222778783465914</v>
+        <v>8.997547827513923</v>
       </c>
     </row>
     <row r="34">
@@ -3248,7 +3248,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>8.239372978888392</v>
+        <v>8.328898843788675</v>
       </c>
     </row>
     <row r="35">
@@ -3256,7 +3256,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>8.233051380632205</v>
+        <v>8.217093009150146</v>
       </c>
     </row>
     <row r="36">
@@ -3264,7 +3264,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>8.244114177580522</v>
+        <v>8.214084133468713</v>
       </c>
     </row>
     <row r="37">
@@ -3272,7 +3272,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>8.259127973438963</v>
+        <v>8.195276175100046</v>
       </c>
     </row>
     <row r="38">
@@ -3280,7 +3280,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>8.242533778016485</v>
+        <v>8.191986499258075</v>
       </c>
     </row>
     <row r="39">
@@ -3288,7 +3288,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>8.253596574964803</v>
+        <v>8.189133967719497</v>
       </c>
     </row>
     <row r="40">
@@ -3296,7 +3296,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>8.259127973438963</v>
+        <v>8.192370324294622</v>
       </c>
     </row>
     <row r="41">
@@ -3304,7 +3304,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>8.293896763847956</v>
+        <v>8.188708512347855</v>
       </c>
     </row>
     <row r="42">
@@ -3312,7 +3312,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>8.259127973438963</v>
+        <v>8.182470105518634</v>
       </c>
     </row>
     <row r="43">
@@ -3320,7 +3320,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>8.263869172131095</v>
+        <v>8.180201707416495</v>
       </c>
     </row>
     <row r="44">
@@ -3328,7 +3328,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>8.265449571695132</v>
+        <v>8.170769637729297</v>
       </c>
     </row>
     <row r="45">
@@ -3336,7 +3336,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>8.263869172131095</v>
+        <v>8.261370299826801</v>
       </c>
     </row>
     <row r="46">
@@ -3344,7 +3344,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>8.265449571695132</v>
+        <v>8.436582548855364</v>
       </c>
     </row>
     <row r="47">
@@ -3352,7 +3352,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>8.261498572785028</v>
+        <v>8.563203879004737</v>
       </c>
     </row>
     <row r="48">
@@ -3360,7 +3360,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>8.259918173220973</v>
+        <v>8.612640344994293</v>
       </c>
     </row>
     <row r="49">
@@ -3368,7 +3368,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>8.264659371913122</v>
+        <v>8.397341929105288</v>
       </c>
     </row>
     <row r="50">
@@ -3376,7 +3376,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>8.248855376272672</v>
+        <v>8.187604339112557</v>
       </c>
     </row>
     <row r="51">
@@ -3384,7 +3384,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>8.169835398070404</v>
+        <v>8.709972511140437</v>
       </c>
     </row>
     <row r="52">
@@ -3392,7 +3392,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>7.751819713380455</v>
+        <v>9.215041836348</v>
       </c>
     </row>
     <row r="53">
@@ -3400,7 +3400,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>7.314839233921961</v>
+        <v>9.338333271919506</v>
       </c>
     </row>
   </sheetData>
@@ -3438,7 +3438,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>3.703862083634493</v>
+        <v>3.526342380134457</v>
       </c>
     </row>
     <row r="3">
@@ -3446,7 +3446,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>3.604498389261747</v>
+        <v>3.526342380134457</v>
       </c>
     </row>
     <row r="4">
@@ -3454,7 +3454,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>3.597463791430061</v>
+        <v>3.526342380134457</v>
       </c>
     </row>
     <row r="5">
@@ -3462,7 +3462,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>3.595705141972125</v>
+        <v>3.528307906894623</v>
       </c>
     </row>
     <row r="6">
@@ -3470,7 +3470,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>3.598343116159009</v>
+        <v>3.541733578511137</v>
       </c>
     </row>
     <row r="7">
@@ -3478,7 +3478,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>3.593946492514208</v>
+        <v>3.550830045967256</v>
       </c>
     </row>
     <row r="8">
@@ -3486,7 +3486,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>3.592187843056272</v>
+        <v>3.548585827106368</v>
       </c>
     </row>
     <row r="9">
@@ -3494,7 +3494,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>3.60273973980383</v>
+        <v>3.549251458095975</v>
       </c>
     </row>
     <row r="10">
@@ -3502,7 +3502,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>3.593946492514208</v>
+        <v>3.548186875626934</v>
       </c>
     </row>
     <row r="11">
@@ -3510,7 +3510,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>3.615050286009305</v>
+        <v>3.549589879466367</v>
       </c>
     </row>
     <row r="12">
@@ -3518,7 +3518,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>3.607136363448631</v>
+        <v>3.551432343910026</v>
       </c>
     </row>
     <row r="13">
@@ -3526,7 +3526,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>3.598343116159009</v>
+        <v>3.55280471564356</v>
       </c>
     </row>
     <row r="14">
@@ -3534,7 +3534,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>3.603619064532798</v>
+        <v>3.551853051525675</v>
       </c>
     </row>
     <row r="15">
@@ -3542,7 +3542,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>3.601860415074862</v>
+        <v>3.551165397453397</v>
       </c>
     </row>
     <row r="16">
@@ -3550,7 +3550,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>3.613291636551369</v>
+        <v>3.551527376848587</v>
       </c>
     </row>
     <row r="17">
@@ -3558,7 +3558,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>3.620326234383074</v>
+        <v>3.55085740797906</v>
       </c>
     </row>
     <row r="18">
@@ -3566,7 +3566,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>3.613291636551369</v>
+        <v>3.549930970301326</v>
       </c>
     </row>
     <row r="19">
@@ -3574,7 +3574,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>3.619446909654106</v>
+        <v>3.546668684391467</v>
       </c>
     </row>
     <row r="20">
@@ -3582,7 +3582,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>3.623843533298927</v>
+        <v>3.537786841886478</v>
       </c>
     </row>
     <row r="21">
@@ -3590,7 +3590,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>3.617688260196189</v>
+        <v>3.52699286191265</v>
       </c>
     </row>
     <row r="22">
@@ -3598,7 +3598,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>3.624722858027895</v>
+        <v>3.515848381241267</v>
       </c>
     </row>
     <row r="23">
@@ -3606,7 +3606,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>3.629119481672696</v>
+        <v>3.411685606917842</v>
       </c>
     </row>
     <row r="24">
@@ -3614,7 +3614,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>3.64670597625194</v>
+        <v>3.480769948424751</v>
       </c>
     </row>
     <row r="25">
@@ -3622,7 +3622,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>3.72496587712959</v>
+        <v>3.383735311859484</v>
       </c>
     </row>
     <row r="26">
@@ -3630,7 +3630,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>4.053833325761496</v>
+        <v>3.356533401192288</v>
       </c>
     </row>
     <row r="27">
@@ -3638,7 +3638,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>4.428425660299428</v>
+        <v>3.356533401192288</v>
       </c>
     </row>
     <row r="28">
@@ -3646,7 +3646,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>4.285095729478572</v>
+        <v>5.059785401192287</v>
       </c>
     </row>
     <row r="29">
@@ -3654,7 +3654,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>4.354562383066599</v>
+        <v>5.059785401192287</v>
       </c>
     </row>
     <row r="30">
@@ -3662,7 +3662,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>4.374786851832728</v>
+        <v>4.938479458897321</v>
       </c>
     </row>
     <row r="31">
@@ -3670,7 +3670,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>4.421391062467722</v>
+        <v>4.457338101878699</v>
       </c>
     </row>
     <row r="32">
@@ -3678,7 +3678,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>4.41787376355187</v>
+        <v>4.479755464467104</v>
       </c>
     </row>
     <row r="33">
@@ -3686,7 +3686,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>4.421391062467722</v>
+        <v>4.422099034031906</v>
       </c>
     </row>
     <row r="34">
@@ -3694,7 +3694,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>4.439856881775935</v>
+        <v>4.414195683763694</v>
       </c>
     </row>
     <row r="35">
@@ -3702,7 +3702,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>4.43282228394423</v>
+        <v>4.401899796288252</v>
       </c>
     </row>
     <row r="36">
@@ -3710,7 +3710,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>4.445132830149704</v>
+        <v>4.400790099868041</v>
       </c>
     </row>
     <row r="37">
@@ -3718,7 +3718,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>4.46184</v>
+        <v>4.401576857812344</v>
       </c>
     </row>
     <row r="38">
@@ -3726,7 +3726,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>4.443374180691787</v>
+        <v>4.401883178871326</v>
       </c>
     </row>
     <row r="39">
@@ -3734,7 +3734,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>4.455684726897262</v>
+        <v>4.402459449534576</v>
       </c>
     </row>
     <row r="40">
@@ -3742,7 +3742,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>4.46184</v>
+        <v>4.402150058591342</v>
       </c>
     </row>
     <row r="41">
@@ -3750,7 +3750,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>4.500530288074341</v>
+        <v>4.401311045878155</v>
       </c>
     </row>
     <row r="42">
@@ -3758,7 +3758,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>4.46184</v>
+        <v>4.401011932373502</v>
       </c>
     </row>
     <row r="43">
@@ -3766,7 +3766,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>4.467115948373769</v>
+        <v>4.401189785450231</v>
       </c>
     </row>
     <row r="44">
@@ -3774,7 +3774,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>4.468874597831685</v>
+        <v>4.401461803889537</v>
       </c>
     </row>
     <row r="45">
@@ -3782,7 +3782,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>4.467115948373769</v>
+        <v>4.400689794736963</v>
       </c>
     </row>
     <row r="46">
@@ -3790,7 +3790,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>4.468874597831685</v>
+        <v>4.397179048412595</v>
       </c>
     </row>
     <row r="47">
@@ -3798,7 +3798,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>4.464477974186885</v>
+        <v>4.384437093408125</v>
       </c>
     </row>
     <row r="48">
@@ -3806,7 +3806,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>4.462719324728949</v>
+        <v>4.346324613902167</v>
       </c>
     </row>
     <row r="49">
@@ -3814,7 +3814,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>4.467995273102737</v>
+        <v>4.507677596674288</v>
       </c>
     </row>
     <row r="50">
@@ -3822,7 +3822,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>4.450408778523493</v>
+        <v>4.186534268950545</v>
       </c>
     </row>
     <row r="51">
@@ -3830,7 +3830,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>4.362476305627253</v>
+        <v>5.010746402796785</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>3.897313524006196</v>
+        <v>5.229594380134457</v>
       </c>
     </row>
     <row r="53">
@@ -3846,7 +3846,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>3.411046948890043</v>
+        <v>5.229594380134457</v>
       </c>
     </row>
   </sheetData>
@@ -3884,7 +3884,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.3303635682898697</v>
+        <v>-0.5039641267274426</v>
       </c>
     </row>
     <row r="3">
@@ -3892,7 +3892,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4251319293885958</v>
+        <v>-0.5093984924204307</v>
       </c>
     </row>
     <row r="4">
@@ -3900,7 +3900,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4318411938911482</v>
+        <v>-0.5172874305507262</v>
       </c>
     </row>
     <row r="5">
@@ -3908,7 +3908,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4335185100168002</v>
+        <v>-0.5185488521780146</v>
       </c>
     </row>
     <row r="6">
@@ -3916,7 +3916,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.4310025358283407</v>
+        <v>-0.506655821282364</v>
       </c>
     </row>
     <row r="7">
@@ -3924,7 +3924,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4351958261424336</v>
+        <v>-0.4932843212412745</v>
       </c>
     </row>
     <row r="8">
@@ -3932,7 +3932,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4368731422680857</v>
+        <v>-0.4805465295209971</v>
       </c>
     </row>
     <row r="9">
@@ -3940,7 +3940,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4268092455142293</v>
+        <v>-0.4749331099005129</v>
       </c>
     </row>
     <row r="10">
@@ -3948,7 +3948,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.4351958261424336</v>
+        <v>-0.4667630804392562</v>
       </c>
     </row>
     <row r="11">
@@ -3956,7 +3956,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4150680326347395</v>
+        <v>-0.4538411263848844</v>
       </c>
     </row>
     <row r="12">
@@ -3964,7 +3964,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4226159552001364</v>
+        <v>-0.4486411623462382</v>
       </c>
     </row>
     <row r="13">
@@ -3972,7 +3972,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4310025358283407</v>
+        <v>-0.4472393980765773</v>
       </c>
     </row>
     <row r="14">
@@ -3980,7 +3980,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.4259705874514033</v>
+        <v>-0.4476664842523243</v>
       </c>
     </row>
     <row r="15">
@@ -3988,7 +3988,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4276479035770553</v>
+        <v>-0.4492842253968948</v>
       </c>
     </row>
     <row r="16">
@@ -3996,7 +3996,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4167453487603915</v>
+        <v>-0.4658176682244434</v>
       </c>
     </row>
     <row r="17">
@@ -4004,7 +4004,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.4100360842578205</v>
+        <v>-0.5258628711528431</v>
       </c>
     </row>
     <row r="18">
@@ -4012,7 +4012,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.4167453487603915</v>
+        <v>-0.5237722107787219</v>
       </c>
     </row>
     <row r="19">
@@ -4020,7 +4020,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.4108747423206466</v>
+        <v>-0.5254910416570647</v>
       </c>
     </row>
     <row r="20">
@@ -4028,7 +4028,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.406681452006535</v>
+        <v>-0.521234070889021</v>
       </c>
     </row>
     <row r="21">
@@ -4036,7 +4036,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.41255205844628</v>
+        <v>-0.5103016256311537</v>
       </c>
     </row>
     <row r="22">
@@ -4044,7 +4044,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.405842793943709</v>
+        <v>-0.5054368279009545</v>
       </c>
     </row>
     <row r="23">
@@ -4052,7 +4052,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.4016495036296162</v>
+        <v>-0.5382165682701892</v>
       </c>
     </row>
     <row r="24">
@@ -4060,7 +4060,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.3848763423732074</v>
+        <v>-0.5142862349093876</v>
       </c>
     </row>
     <row r="25">
@@ -4068,7 +4068,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.3102357747821755</v>
+        <v>-0.5968184289838053</v>
       </c>
     </row>
     <row r="26">
@@ -4076,7 +4076,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>0.003422340712709027</v>
+        <v>-0.7127857314199553</v>
       </c>
     </row>
     <row r="27">
@@ -4084,7 +4084,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>0.3606906754742488</v>
+        <v>-0.9601654374792454</v>
       </c>
     </row>
     <row r="28">
@@ -4092,7 +4092,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2239894112345008</v>
+        <v>0.7315266803331284</v>
       </c>
     </row>
     <row r="29">
@@ -4100,7 +4100,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2902433981973284</v>
+        <v>0.6324362647882658</v>
       </c>
     </row>
     <row r="30">
@@ -4108,7 +4108,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3095325336421966</v>
+        <v>0.5862784234552012</v>
       </c>
     </row>
     <row r="31">
@@ -4116,7 +4116,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3539814109716778</v>
+        <v>0.3763281536602175</v>
       </c>
     </row>
     <row r="32">
@@ -4124,7 +4124,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3506267787203924</v>
+        <v>0.3796352427385145</v>
       </c>
     </row>
     <row r="33">
@@ -4132,7 +4132,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3539814109716778</v>
+        <v>0.3514905684279914</v>
       </c>
     </row>
     <row r="34">
@@ -4140,7 +4140,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>0.3715932302909126</v>
+        <v>0.3436730814091082</v>
       </c>
     </row>
     <row r="35">
@@ -4148,7 +4148,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3648839657883417</v>
+        <v>0.3348289715075891</v>
       </c>
     </row>
     <row r="36">
@@ -4156,7 +4156,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3766251786678315</v>
+        <v>0.3331893234998242</v>
       </c>
     </row>
     <row r="37">
@@ -4164,7 +4164,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3925596818614329</v>
+        <v>0.333947974545635</v>
       </c>
     </row>
     <row r="38">
@@ -4172,7 +4172,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>0.3749478625421981</v>
+        <v>0.3344172645781615</v>
       </c>
     </row>
     <row r="39">
@@ -4180,7 +4180,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>0.386689075421688</v>
+        <v>0.3350769404617849</v>
       </c>
     </row>
     <row r="40">
@@ -4188,7 +4188,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>0.3925596818614329</v>
+        <v>0.3353766193246073</v>
       </c>
     </row>
     <row r="41">
@@ -4196,7 +4196,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>0.4294606366255358</v>
+        <v>0.3353746917663612</v>
       </c>
     </row>
     <row r="42">
@@ -4204,7 +4204,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>0.3925596818614329</v>
+        <v>0.3355154467042921</v>
       </c>
     </row>
     <row r="43">
@@ -4212,7 +4212,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3975916302383518</v>
+        <v>0.3357487890335164</v>
       </c>
     </row>
     <row r="44">
@@ -4220,7 +4220,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>0.3992689463639852</v>
+        <v>0.3433100674593284</v>
       </c>
     </row>
     <row r="45">
@@ -4228,7 +4228,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3975916302383518</v>
+        <v>0.3344592131218199</v>
       </c>
     </row>
     <row r="46">
@@ -4236,7 +4236,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3992689463639852</v>
+        <v>0.3230732241042686</v>
       </c>
     </row>
     <row r="47">
@@ -4244,7 +4244,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>0.3950756560498923</v>
+        <v>0.3198989150893806</v>
       </c>
     </row>
     <row r="48">
@@ -4252,7 +4252,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3933983399242403</v>
+        <v>0.3302405053998392</v>
       </c>
     </row>
     <row r="49">
@@ -4260,7 +4260,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>0.3984302883011778</v>
+        <v>0.4050345750712405</v>
       </c>
     </row>
     <row r="50">
@@ -4268,7 +4268,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>0.3816571270447691</v>
+        <v>0.2784337529939935</v>
       </c>
     </row>
     <row r="51">
@@ -4276,7 +4276,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>0.2977913207627067</v>
+        <v>0.7572079601207087</v>
       </c>
     </row>
     <row r="52">
@@ -4284,7 +4284,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.1458587944693549</v>
+        <v>0.9956878531071215</v>
       </c>
     </row>
     <row r="53">
@@ -4292,7 +4292,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.6096367032091107</v>
+        <v>1.126121971149564</v>
       </c>
     </row>
   </sheetData>

--- a/SOT_results/SOT_all_angles_52point.xlsx
+++ b/SOT_results/SOT_all_angles_52point.xlsx
@@ -459,7 +459,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>17.47943486872997</v>
+        <v>16.8834155</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>17.10272421664234</v>
+        <v>16.8834155</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>16.80418393457441</v>
+        <v>16.8834155</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>16.83684697057579</v>
+        <v>16.8834155</v>
       </c>
     </row>
     <row r="6">
@@ -491,7 +491,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>16.89469536107498</v>
+        <v>16.88341550000001</v>
       </c>
     </row>
     <row r="7">
@@ -499,7 +499,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>16.89952936182164</v>
+        <v>16.88341550000003</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>16.87219303771848</v>
+        <v>16.88341550000014</v>
       </c>
     </row>
     <row r="9">
@@ -515,7 +515,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>16.87124308618445</v>
+        <v>16.88341550000075</v>
       </c>
     </row>
     <row r="10">
@@ -523,7 +523,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>16.87043280080362</v>
+        <v>16.88341550000388</v>
       </c>
     </row>
     <row r="11">
@@ -531,7 +531,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>16.86388013044959</v>
+        <v>16.88341550002017</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +539,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>16.85969901354604</v>
+        <v>16.88341550010473</v>
       </c>
     </row>
     <row r="13">
@@ -547,7 +547,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>16.86149527546073</v>
+        <v>16.88341550054375</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>16.86003709431369</v>
+        <v>16.883415502823</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>16.85898959816473</v>
+        <v>16.88341551465612</v>
       </c>
     </row>
     <row r="16">
@@ -571,7 +571,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>16.85777638701655</v>
+        <v>16.88341557608996</v>
       </c>
     </row>
     <row r="17">
@@ -579,7 +579,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>17.04785370805233</v>
+        <v>16.88341589503457</v>
       </c>
     </row>
     <row r="18">
@@ -587,7 +587,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>17.37541074190787</v>
+        <v>16.88341755087551</v>
       </c>
     </row>
     <row r="19">
@@ -595,7 +595,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>17.57173479791449</v>
+        <v>16.88342614694968</v>
       </c>
     </row>
     <row r="20">
@@ -603,7 +603,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>17.58320127824558</v>
+        <v>16.88347076067125</v>
       </c>
     </row>
     <row r="21">
@@ -611,7 +611,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>17.57560166597336</v>
+        <v>16.88370199342717</v>
       </c>
     </row>
     <row r="22">
@@ -619,7 +619,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>17.5380569653794</v>
+        <v>16.88489212332209</v>
       </c>
     </row>
     <row r="23">
@@ -627,7 +627,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>17.48530971485639</v>
+        <v>16.89080413996444</v>
       </c>
     </row>
     <row r="24">
@@ -635,7 +635,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>17.10180253087741</v>
+        <v>16.91570608723391</v>
       </c>
     </row>
     <row r="25">
@@ -643,7 +643,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>17.3916253172168</v>
+        <v>16.97545676069531</v>
       </c>
     </row>
     <row r="26">
@@ -651,7 +651,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>17.59302945243047</v>
+        <v>17.02642929636333</v>
       </c>
     </row>
     <row r="27">
@@ -659,7 +659,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>17.40216013562916</v>
+        <v>17.04350629231351</v>
       </c>
     </row>
     <row r="28">
@@ -667,7 +667,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>17.40497230253911</v>
+        <v>17.0482005</v>
       </c>
     </row>
     <row r="29">
@@ -675,7 +675,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>17.4892259094535</v>
+        <v>17.0482005</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>17.41097185058803</v>
+        <v>17.0482005</v>
       </c>
     </row>
     <row r="31">
@@ -691,7 +691,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>17.64260871989134</v>
+        <v>17.0482005</v>
       </c>
     </row>
     <row r="32">
@@ -699,7 +699,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>17.65801744366556</v>
+        <v>17.04820049999999</v>
       </c>
     </row>
     <row r="33">
@@ -707,7 +707,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>17.54056596805999</v>
+        <v>17.04820049999997</v>
       </c>
     </row>
     <row r="34">
@@ -715,7 +715,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>17.1117071889081</v>
+        <v>17.04820049999985</v>
       </c>
     </row>
     <row r="35">
@@ -723,7 +723,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>17.04424400306918</v>
+        <v>17.04820049999925</v>
       </c>
     </row>
     <row r="36">
@@ -731,7 +731,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>17.04272984461471</v>
+        <v>17.04820049999611</v>
       </c>
     </row>
     <row r="37">
@@ -739,7 +739,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>17.03027627928823</v>
+        <v>17.04820049997982</v>
       </c>
     </row>
     <row r="38">
@@ -747,7 +747,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>17.02803275314485</v>
+        <v>17.04820049989526</v>
       </c>
     </row>
     <row r="39">
@@ -755,7 +755,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>17.02596713507758</v>
+        <v>17.04820049945624</v>
       </c>
     </row>
     <row r="40">
@@ -763,7 +763,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>17.02817740737495</v>
+        <v>17.048200497177</v>
       </c>
     </row>
     <row r="41">
@@ -771,7 +771,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>17.02613672969217</v>
+        <v>17.04820048534388</v>
       </c>
     </row>
     <row r="42">
@@ -779,7 +779,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>17.02222275201813</v>
+        <v>17.04820042391003</v>
       </c>
     </row>
     <row r="43">
@@ -787,7 +787,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>17.02068864125606</v>
+        <v>17.04820010496543</v>
       </c>
     </row>
     <row r="44">
@@ -795,7 +795,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>17.01449067859268</v>
+        <v>17.04819844912449</v>
       </c>
     </row>
     <row r="45">
@@ -803,7 +803,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>17.07331340677963</v>
+        <v>17.04818985305032</v>
       </c>
     </row>
     <row r="46">
@@ -811,7 +811,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>17.18785129124496</v>
+        <v>17.04814523932875</v>
       </c>
     </row>
     <row r="47">
@@ -819,7 +819,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>17.27457399622474</v>
+        <v>17.04791400657282</v>
       </c>
     </row>
     <row r="48">
@@ -827,7 +827,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>17.32125685369913</v>
+        <v>17.04672387667791</v>
       </c>
     </row>
     <row r="49">
@@ -835,7 +835,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>17.11974187233213</v>
+        <v>17.04081186003555</v>
       </c>
     </row>
     <row r="50">
@@ -843,7 +843,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>17.10853976007673</v>
+        <v>17.01590991276608</v>
       </c>
     </row>
     <row r="51">
@@ -851,7 +851,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>17.12700506652899</v>
+        <v>16.95615923930469</v>
       </c>
     </row>
     <row r="52">
@@ -859,7 +859,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>17.36856543770906</v>
+        <v>16.90518670363667</v>
       </c>
     </row>
     <row r="53">
@@ -867,7 +867,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>17.44820618195268</v>
+        <v>16.88810970768649</v>
       </c>
     </row>
   </sheetData>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.164785（保持前次角度模型）</t>
+          <t>0.164785</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.5263596444（保持前次角度模型）</t>
+          <t>0.5263596444</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.7653084889（保持前次角度模型）</t>
+          <t>0.7653084889</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.851626（保持前次角度模型）</t>
+          <t>0.851626</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.8122403338（保持前次角度模型）</t>
+          <t>0.8122403338</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2546,7 +2546,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>13.17773356095276</v>
+        <v>11.9258011778</v>
       </c>
     </row>
     <row r="3">
@@ -2554,7 +2554,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>12.37553560654939</v>
+        <v>11.9258011778</v>
       </c>
     </row>
     <row r="4">
@@ -2562,7 +2562,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>11.73979992385841</v>
+        <v>11.9258011778</v>
       </c>
     </row>
     <row r="5">
@@ -2570,7 +2570,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>11.80976015985502</v>
+        <v>11.92580117780001</v>
       </c>
     </row>
     <row r="6">
@@ -2578,7 +2578,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>11.93571315045511</v>
+        <v>11.92580117780004</v>
       </c>
     </row>
     <row r="7">
@@ -2586,7 +2586,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>11.9478811276776</v>
+        <v>11.92580117780022</v>
       </c>
     </row>
     <row r="8">
@@ -2594,7 +2594,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>11.88920660377777</v>
+        <v>11.92580117780111</v>
       </c>
     </row>
     <row r="9">
@@ -2602,7 +2602,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>11.88732083484917</v>
+        <v>11.92580117780578</v>
       </c>
     </row>
     <row r="10">
@@ -2610,7 +2610,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>11.88537602118982</v>
+        <v>11.92580117782999</v>
       </c>
     </row>
     <row r="11">
@@ -2618,7 +2618,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>11.87171128689949</v>
+        <v>11.92580117795572</v>
       </c>
     </row>
     <row r="12">
@@ -2626,7 +2626,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>11.8631872675331</v>
+        <v>11.92580117860846</v>
       </c>
     </row>
     <row r="13">
@@ -2634,7 +2634,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>11.86729511009491</v>
+        <v>11.92580118199728</v>
       </c>
     </row>
     <row r="14">
@@ -2642,7 +2642,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>11.86399387869406</v>
+        <v>11.92580119959096</v>
       </c>
     </row>
     <row r="15">
@@ -2650,7 +2650,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>11.86162158468165</v>
+        <v>11.92580129093184</v>
       </c>
     </row>
     <row r="16">
@@ -2658,7 +2658,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>11.85911265082287</v>
+        <v>11.92580176514466</v>
       </c>
     </row>
     <row r="17">
@@ -2666,7 +2666,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>12.26374055467733</v>
+        <v>11.92580422709577</v>
       </c>
     </row>
     <row r="18">
@@ -2674,7 +2674,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>12.96107597587945</v>
+        <v>11.92581700840688</v>
       </c>
     </row>
     <row r="19">
@@ -2682,7 +2682,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>13.37847210660041</v>
+        <v>11.92588335500683</v>
       </c>
     </row>
     <row r="20">
@@ -2690,7 +2690,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>13.40105990187159</v>
+        <v>11.92622753717346</v>
       </c>
     </row>
     <row r="21">
@@ -2698,7 +2698,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>13.38265288510657</v>
+        <v>11.9280072122887</v>
       </c>
     </row>
     <row r="22">
@@ -2706,7 +2706,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>13.30040617868298</v>
+        <v>11.93705648826432</v>
       </c>
     </row>
     <row r="23">
@@ -2714,7 +2714,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>13.16662217718366</v>
+        <v>11.97942850213443</v>
       </c>
     </row>
     <row r="24">
@@ -2722,7 +2722,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>12.36418399676562</v>
+        <v>12.1208985354515</v>
       </c>
     </row>
     <row r="25">
@@ -2730,7 +2730,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>12.96136472751776</v>
+        <v>12.322440545419</v>
       </c>
     </row>
     <row r="26">
@@ -2738,7 +2738,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>13.3846467114349</v>
+        <v>12.42096797572261</v>
       </c>
     </row>
     <row r="27">
@@ -2746,7 +2746,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>12.97819424016057</v>
+        <v>12.44585067323093</v>
       </c>
     </row>
     <row r="28">
@@ -2754,7 +2754,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>13.33508912410903</v>
+        <v>12.4521608222</v>
       </c>
     </row>
     <row r="29">
@@ -2762,7 +2762,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>13.51450552962682</v>
+        <v>12.4521608222</v>
       </c>
     </row>
     <row r="30">
@@ -2770,7 +2770,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>13.3228734192533</v>
+        <v>12.4521608222</v>
       </c>
     </row>
     <row r="31">
@@ -2778,7 +2778,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>13.71701415982138</v>
+        <v>12.45216082219999</v>
       </c>
     </row>
     <row r="32">
@@ -2786,7 +2786,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>13.75444519258381</v>
+        <v>12.45216082219996</v>
       </c>
     </row>
     <row r="33">
@@ -2794,7 +2794,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>13.49245611516705</v>
+        <v>12.45216082219979</v>
       </c>
     </row>
     <row r="34">
@@ -2802,7 +2802,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>12.57758148608428</v>
+        <v>12.45216082219889</v>
       </c>
     </row>
     <row r="35">
@@ -2810,7 +2810,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>12.43138673690372</v>
+        <v>12.45216082219422</v>
       </c>
     </row>
     <row r="36">
@@ -2818,7 +2818,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>12.42793374488073</v>
+        <v>12.45216082217001</v>
       </c>
     </row>
     <row r="37">
@@ -2826,7 +2826,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>12.4015762104699</v>
+        <v>12.45216082204428</v>
       </c>
     </row>
     <row r="38">
@@ -2834,7 +2834,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>12.39686177420067</v>
+        <v>12.45216082139154</v>
       </c>
     </row>
     <row r="39">
@@ -2842,7 +2842,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>12.3925818051007</v>
+        <v>12.45216081800272</v>
       </c>
     </row>
     <row r="40">
@@ -2850,7 +2850,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>12.39722479549429</v>
+        <v>12.45216080040904</v>
       </c>
     </row>
     <row r="41">
@@ -2858,7 +2858,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>12.39270635773545</v>
+        <v>12.45216070906816</v>
       </c>
     </row>
     <row r="42">
@@ -2866,7 +2866,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>12.38430999515282</v>
+        <v>12.45216023485534</v>
       </c>
     </row>
     <row r="43">
@@ -2874,7 +2874,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>12.38107977788297</v>
+        <v>12.45215777290423</v>
       </c>
     </row>
     <row r="44">
@@ -2882,7 +2882,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>12.36793737943099</v>
+        <v>12.45214499159312</v>
       </c>
     </row>
     <row r="45">
@@ -2890,7 +2890,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>12.49304017641562</v>
+        <v>12.45207864499317</v>
       </c>
     </row>
     <row r="46">
@@ -2898,7 +2898,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>12.73622306873994</v>
+        <v>12.45173446282654</v>
       </c>
     </row>
     <row r="47">
@@ -2906,7 +2906,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>12.91827225430441</v>
+        <v>12.4499547877113</v>
       </c>
     </row>
     <row r="48">
@@ -2914,7 +2914,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>13.00983049693937</v>
+        <v>12.44090551173568</v>
       </c>
     </row>
     <row r="49">
@@ -2922,7 +2922,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>12.61395046535296</v>
+        <v>12.39853349786557</v>
       </c>
     </row>
     <row r="50">
@@ -2930,7 +2930,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>12.52393337593741</v>
+        <v>12.25706346454851</v>
       </c>
     </row>
     <row r="51">
@@ -2938,7 +2938,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>12.73306025493985</v>
+        <v>12.055521454581</v>
       </c>
     </row>
     <row r="52">
@@ -2946,7 +2946,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>13.29254570896565</v>
+        <v>11.95699402427739</v>
       </c>
     </row>
     <row r="53">
@@ -2954,7 +2954,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>13.46213911378534</v>
+        <v>11.93211132676907</v>
       </c>
     </row>
   </sheetData>
@@ -2992,7 +2992,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>8.366266926306173</v>
+        <v>7.49381975555</v>
       </c>
     </row>
     <row r="3">
@@ -3000,7 +3000,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>7.783083060659582</v>
+        <v>7.493819755550001</v>
       </c>
     </row>
     <row r="4">
@@ -3008,7 +3008,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>7.32091435164443</v>
+        <v>7.493819755550004</v>
       </c>
     </row>
     <row r="5">
@@ -3016,7 +3016,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>7.372657372439897</v>
+        <v>7.493819755550022</v>
       </c>
     </row>
     <row r="6">
@@ -3024,7 +3024,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>7.47025543984111</v>
+        <v>7.493819755550114</v>
       </c>
     </row>
     <row r="7">
@@ -3032,7 +3032,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>7.483188588592592</v>
+        <v>7.493819755550594</v>
       </c>
     </row>
     <row r="8">
@@ -3040,7 +3040,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>7.439524860393856</v>
+        <v>7.493819755553086</v>
       </c>
     </row>
     <row r="9">
@@ -3048,7 +3048,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>7.43845302201026</v>
+        <v>7.493819755566025</v>
       </c>
     </row>
     <row r="10">
@@ -3056,7 +3056,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>7.436560836277589</v>
+        <v>7.493819755633199</v>
       </c>
     </row>
     <row r="11">
@@ -3064,7 +3064,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>7.42725721413388</v>
+        <v>7.493819755981944</v>
       </c>
     </row>
     <row r="12">
@@ -3072,7 +3072,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>7.421888261011556</v>
+        <v>7.493819757792517</v>
       </c>
     </row>
     <row r="13">
@@ -3080,7 +3080,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>7.425491227348444</v>
+        <v>7.493819767192449</v>
       </c>
     </row>
     <row r="14">
@@ -3088,7 +3088,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>7.422663686362126</v>
+        <v>7.493819815993961</v>
       </c>
     </row>
     <row r="15">
@@ -3096,7 +3096,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>7.420630092095929</v>
+        <v>7.493820069356063</v>
       </c>
     </row>
     <row r="16">
@@ -3104,7 +3104,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>7.418968786397502</v>
+        <v>7.493821384730269</v>
       </c>
     </row>
     <row r="17">
@@ -3112,7 +3112,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>7.712825155392096</v>
+        <v>7.493828213669662</v>
       </c>
     </row>
     <row r="18">
@@ -3120,7 +3120,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>8.219359526865805</v>
+        <v>7.493863665431471</v>
       </c>
     </row>
     <row r="19">
@@ -3128,7 +3128,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>8.521333388293762</v>
+        <v>7.494047667127988</v>
       </c>
     </row>
     <row r="20">
@@ -3136,7 +3136,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>8.533763513239384</v>
+        <v>7.495001526078109</v>
       </c>
     </row>
     <row r="21">
@@ -3144,7 +3144,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>8.515531962378061</v>
+        <v>7.499915681933166</v>
       </c>
     </row>
     <row r="22">
@@ -3152,7 +3152,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>8.450732587372531</v>
+        <v>7.524445369465496</v>
       </c>
     </row>
     <row r="23">
@@ -3160,7 +3160,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>8.306671341373042</v>
+        <v>7.629978997786136</v>
       </c>
     </row>
     <row r="24">
@@ -3168,7 +3168,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>7.754353945805643</v>
+        <v>7.898741373873175</v>
       </c>
     </row>
     <row r="25">
@@ -3176,7 +3176,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>8.144894088974961</v>
+        <v>8.147130508230694</v>
       </c>
     </row>
     <row r="26">
@@ -3184,7 +3184,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>8.44039026402805</v>
+        <v>8.23466530959443</v>
       </c>
     </row>
     <row r="27">
@@ -3192,7 +3192,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>8.144906434758418</v>
+        <v>8.254291474969587</v>
       </c>
     </row>
     <row r="28">
@@ -3200,7 +3200,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>9.169671254739878</v>
+        <v>8.25912824445</v>
       </c>
     </row>
     <row r="29">
@@ -3208,7 +3208,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>9.300103839809365</v>
+        <v>8.259128244449998</v>
       </c>
     </row>
     <row r="30">
@@ -3216,7 +3216,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>9.106285230180562</v>
+        <v>8.259128244449995</v>
       </c>
     </row>
     <row r="31">
@@ -3224,7 +3224,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>9.176631280010083</v>
+        <v>8.259128244449977</v>
       </c>
     </row>
     <row r="32">
@@ -3232,7 +3232,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>9.213915598172079</v>
+        <v>8.259128244449885</v>
       </c>
     </row>
     <row r="33">
@@ -3240,7 +3240,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>8.997547827513923</v>
+        <v>8.259128244449405</v>
       </c>
     </row>
     <row r="34">
@@ -3248,7 +3248,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>8.328898843788675</v>
+        <v>8.259128244446913</v>
       </c>
     </row>
     <row r="35">
@@ -3256,7 +3256,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>8.217093009150146</v>
+        <v>8.259128244433974</v>
       </c>
     </row>
     <row r="36">
@@ -3264,7 +3264,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>8.214084133468713</v>
+        <v>8.259128244366801</v>
       </c>
     </row>
     <row r="37">
@@ -3272,7 +3272,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>8.195276175100046</v>
+        <v>8.259128244018056</v>
       </c>
     </row>
     <row r="38">
@@ -3280,7 +3280,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>8.191986499258075</v>
+        <v>8.259128242207483</v>
       </c>
     </row>
     <row r="39">
@@ -3288,7 +3288,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>8.189133967719497</v>
+        <v>8.25912823280755</v>
       </c>
     </row>
     <row r="40">
@@ -3296,7 +3296,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>8.192370324294622</v>
+        <v>8.259128184006039</v>
       </c>
     </row>
     <row r="41">
@@ -3304,7 +3304,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>8.188708512347855</v>
+        <v>8.259127930643936</v>
       </c>
     </row>
     <row r="42">
@@ -3312,7 +3312,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>8.182470105518634</v>
+        <v>8.25912661526973</v>
       </c>
     </row>
     <row r="43">
@@ -3320,7 +3320,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>8.180201707416495</v>
+        <v>8.259119786330338</v>
       </c>
     </row>
     <row r="44">
@@ -3328,7 +3328,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>8.170769637729297</v>
+        <v>8.259084334568529</v>
       </c>
     </row>
     <row r="45">
@@ -3336,7 +3336,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>8.261370299826801</v>
+        <v>8.258900332872011</v>
       </c>
     </row>
     <row r="46">
@@ -3344,7 +3344,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>8.436582548855364</v>
+        <v>8.257946473921889</v>
       </c>
     </row>
     <row r="47">
@@ -3352,7 +3352,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>8.563203879004737</v>
+        <v>8.253032318066834</v>
       </c>
     </row>
     <row r="48">
@@ -3360,7 +3360,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>8.612640344994293</v>
+        <v>8.228502630534503</v>
       </c>
     </row>
     <row r="49">
@@ -3368,7 +3368,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>8.397341929105288</v>
+        <v>8.122969002213864</v>
       </c>
     </row>
     <row r="50">
@@ -3376,7 +3376,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>8.187604339112557</v>
+        <v>7.854206626126825</v>
       </c>
     </row>
     <row r="51">
@@ -3384,7 +3384,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>8.709972511140437</v>
+        <v>7.605817491769306</v>
       </c>
     </row>
     <row r="52">
@@ -3392,7 +3392,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>9.215041836348</v>
+        <v>7.51828269040557</v>
       </c>
     </row>
     <row r="53">
@@ -3400,7 +3400,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>9.338333271919506</v>
+        <v>7.498656525030412</v>
       </c>
     </row>
   </sheetData>
@@ -3438,7 +3438,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214</v>
       </c>
     </row>
     <row r="3">
@@ -3446,7 +3446,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3454,7 +3454,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214000000006</v>
       </c>
     </row>
     <row r="5">
@@ -3462,7 +3462,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>3.528307906894623</v>
+        <v>3.610214000000031</v>
       </c>
     </row>
     <row r="6">
@@ -3470,7 +3470,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>3.541733578511137</v>
+        <v>3.610214000000162</v>
       </c>
     </row>
     <row r="7">
@@ -3478,7 +3478,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>3.550830045967256</v>
+        <v>3.610214000000838</v>
       </c>
     </row>
     <row r="8">
@@ -3486,7 +3486,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>3.548585827106368</v>
+        <v>3.610214000004351</v>
       </c>
     </row>
     <row r="9">
@@ -3494,7 +3494,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549251458095975</v>
+        <v>3.610214000022589</v>
       </c>
     </row>
     <row r="10">
@@ -3502,7 +3502,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>3.548186875626934</v>
+        <v>3.610214000117276</v>
       </c>
     </row>
     <row r="11">
@@ -3510,7 +3510,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>3.549589879466367</v>
+        <v>3.610214000608861</v>
       </c>
     </row>
     <row r="12">
@@ -3518,7 +3518,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>3.551432343910026</v>
+        <v>3.610214003161015</v>
       </c>
     </row>
     <row r="13">
@@ -3526,7 +3526,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>3.55280471564356</v>
+        <v>3.610214016411005</v>
       </c>
     </row>
     <row r="14">
@@ -3534,7 +3534,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>3.551853051525675</v>
+        <v>3.610214085200803</v>
       </c>
     </row>
     <row r="15">
@@ -3542,7 +3542,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>3.551165397453397</v>
+        <v>3.610214442335776</v>
       </c>
     </row>
     <row r="16">
@@ -3550,7 +3550,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>3.551527376848587</v>
+        <v>3.610216296464196</v>
       </c>
     </row>
     <row r="17">
@@ -3558,7 +3558,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>3.55085740797906</v>
+        <v>3.610225922390113</v>
       </c>
     </row>
     <row r="18">
@@ -3566,7 +3566,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>3.549930970301326</v>
+        <v>3.610275893693837</v>
       </c>
     </row>
     <row r="19">
@@ -3574,7 +3574,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>3.546668684391467</v>
+        <v>3.610535234866895</v>
       </c>
     </row>
     <row r="20">
@@ -3582,7 +3582,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>3.537786841886478</v>
+        <v>3.61187911836197</v>
       </c>
     </row>
     <row r="21">
@@ -3590,7 +3590,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>3.52699286191265</v>
+        <v>3.618788500603038</v>
       </c>
     </row>
     <row r="22">
@@ -3598,7 +3598,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>3.515848381241267</v>
+        <v>3.652927469688595</v>
       </c>
     </row>
     <row r="23">
@@ -3606,7 +3606,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>3.411685606917842</v>
+        <v>3.793447015792268</v>
       </c>
     </row>
     <row r="24">
@@ -3614,7 +3614,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>3.480769948424751</v>
+        <v>4.110400030319937</v>
       </c>
     </row>
     <row r="25">
@@ -3622,7 +3622,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>3.383735311859484</v>
+        <v>4.360323692329992</v>
       </c>
     </row>
     <row r="26">
@@ -3630,7 +3630,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>3.356533401192288</v>
+        <v>4.440204079390156</v>
       </c>
     </row>
     <row r="27">
@@ -3638,7 +3638,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>3.356533401192288</v>
+        <v>4.457585312412417</v>
       </c>
     </row>
     <row r="28">
@@ -3646,7 +3646,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>5.059785401192287</v>
+        <v>4.46184</v>
       </c>
     </row>
     <row r="29">
@@ -3654,7 +3654,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>5.059785401192287</v>
+        <v>4.461839999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3662,7 +3662,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>4.938479458897321</v>
+        <v>4.461839999999994</v>
       </c>
     </row>
     <row r="31">
@@ -3670,7 +3670,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>4.457338101878699</v>
+        <v>4.461839999999969</v>
       </c>
     </row>
     <row r="32">
@@ -3678,7 +3678,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>4.479755464467104</v>
+        <v>4.461839999999839</v>
       </c>
     </row>
     <row r="33">
@@ -3686,7 +3686,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>4.422099034031906</v>
+        <v>4.461839999999162</v>
       </c>
     </row>
     <row r="34">
@@ -3694,7 +3694,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>4.414195683763694</v>
+        <v>4.461839999995649</v>
       </c>
     </row>
     <row r="35">
@@ -3702,7 +3702,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>4.401899796288252</v>
+        <v>4.461839999977411</v>
       </c>
     </row>
     <row r="36">
@@ -3710,7 +3710,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>4.400790099868041</v>
+        <v>4.461839999882724</v>
       </c>
     </row>
     <row r="37">
@@ -3718,7 +3718,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>4.401576857812344</v>
+        <v>4.461839999391139</v>
       </c>
     </row>
     <row r="38">
@@ -3726,7 +3726,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>4.401883178871326</v>
+        <v>4.461839996838984</v>
       </c>
     </row>
     <row r="39">
@@ -3734,7 +3734,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>4.402459449534576</v>
+        <v>4.461839983588995</v>
       </c>
     </row>
     <row r="40">
@@ -3742,7 +3742,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>4.402150058591342</v>
+        <v>4.461839914799197</v>
       </c>
     </row>
     <row r="41">
@@ -3750,7 +3750,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>4.401311045878155</v>
+        <v>4.461839557664224</v>
       </c>
     </row>
     <row r="42">
@@ -3758,7 +3758,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>4.401011932373502</v>
+        <v>4.461837703535804</v>
       </c>
     </row>
     <row r="43">
@@ -3766,7 +3766,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>4.401189785450231</v>
+        <v>4.461828077609887</v>
       </c>
     </row>
     <row r="44">
@@ -3774,7 +3774,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>4.401461803889537</v>
+        <v>4.461778106306164</v>
       </c>
     </row>
     <row r="45">
@@ -3782,7 +3782,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>4.400689794736963</v>
+        <v>4.461518765133105</v>
       </c>
     </row>
     <row r="46">
@@ -3790,7 +3790,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>4.397179048412595</v>
+        <v>4.46017488163803</v>
       </c>
     </row>
     <row r="47">
@@ -3798,7 +3798,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>4.384437093408125</v>
+        <v>4.453265499396961</v>
       </c>
     </row>
     <row r="48">
@@ -3806,7 +3806,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>4.346324613902167</v>
+        <v>4.419126530311405</v>
       </c>
     </row>
     <row r="49">
@@ -3814,7 +3814,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>4.507677596674288</v>
+        <v>4.278606984207732</v>
       </c>
     </row>
     <row r="50">
@@ -3822,7 +3822,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>4.186534268950545</v>
+        <v>3.961653969680063</v>
       </c>
     </row>
     <row r="51">
@@ -3830,7 +3830,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>5.010746402796785</v>
+        <v>3.711730307670008</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>5.229594380134457</v>
+        <v>3.631849920609843</v>
       </c>
     </row>
     <row r="53">
@@ -3846,7 +3846,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>5.229594380134457</v>
+        <v>3.614468687587583</v>
       </c>
     </row>
   </sheetData>
@@ -3884,7 +3884,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5039641267274426</v>
+        <v>-0.4196801668999999</v>
       </c>
     </row>
     <row r="3">
@@ -3892,7 +3892,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.5093984924204307</v>
+        <v>-0.4196801668999992</v>
       </c>
     </row>
     <row r="4">
@@ -3900,7 +3900,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.5172874305507262</v>
+        <v>-0.4196801668999955</v>
       </c>
     </row>
     <row r="5">
@@ -3908,7 +3908,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.5185488521780146</v>
+        <v>-0.4196801668999766</v>
       </c>
     </row>
     <row r="6">
@@ -3916,7 +3916,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.506655821282364</v>
+        <v>-0.4196801668998785</v>
       </c>
     </row>
     <row r="7">
@@ -3924,7 +3924,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4932843212412745</v>
+        <v>-0.419680166899369</v>
       </c>
     </row>
     <row r="8">
@@ -3932,7 +3932,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4805465295209971</v>
+        <v>-0.419680166896724</v>
       </c>
     </row>
     <row r="9">
@@ -3940,7 +3940,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4749331099005129</v>
+        <v>-0.4196801668829919</v>
       </c>
     </row>
     <row r="10">
@@ -3948,7 +3948,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.4667630804392562</v>
+        <v>-0.4196801668116988</v>
       </c>
     </row>
     <row r="11">
@@ -3956,7 +3956,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4538411263848844</v>
+        <v>-0.4196801664415676</v>
       </c>
     </row>
     <row r="12">
@@ -3964,7 +3964,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4486411623462382</v>
+        <v>-0.4196801645199623</v>
       </c>
     </row>
     <row r="13">
@@ -3972,7 +3972,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4472393980765773</v>
+        <v>-0.4196801545435873</v>
       </c>
     </row>
     <row r="14">
@@ -3980,7 +3980,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.4476664842523243</v>
+        <v>-0.4196801027493685</v>
       </c>
     </row>
     <row r="15">
@@ -3988,7 +3988,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4492842253968948</v>
+        <v>-0.4196798338500667</v>
       </c>
     </row>
     <row r="16">
@@ -3996,7 +3996,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4658176682244434</v>
+        <v>-0.4196784378117364</v>
       </c>
     </row>
     <row r="17">
@@ -4004,7 +4004,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.5258628711528431</v>
+        <v>-0.4196711900938659</v>
       </c>
     </row>
     <row r="18">
@@ -4012,7 +4012,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.5237722107787219</v>
+        <v>-0.4196335642851063</v>
       </c>
     </row>
     <row r="19">
@@ -4020,7 +4020,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.5254910416570647</v>
+        <v>-0.4194382788524134</v>
       </c>
     </row>
     <row r="20">
@@ -4028,7 +4028,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.521234070889021</v>
+        <v>-0.4184259253723688</v>
       </c>
     </row>
     <row r="21">
@@ -4036,7 +4036,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.5103016256311537</v>
+        <v>-0.4132104133926276</v>
       </c>
     </row>
     <row r="22">
@@ -4044,7 +4044,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.5054368279009545</v>
+        <v>-0.3871764651505178</v>
       </c>
     </row>
     <row r="23">
@@ -4052,7 +4052,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.5382165682701892</v>
+        <v>-0.275171083350183</v>
       </c>
     </row>
     <row r="24">
@@ -4060,7 +4060,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.5142862349093876</v>
+        <v>0.01007290026168889</v>
       </c>
     </row>
     <row r="25">
@@ -4068,7 +4068,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.5968184289838053</v>
+        <v>0.2736942716812417</v>
       </c>
     </row>
     <row r="26">
@@ -4076,7 +4076,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.7127857314199553</v>
+        <v>0.3665970648816554</v>
       </c>
     </row>
     <row r="27">
@@ -4084,7 +4084,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.9601654374792454</v>
+        <v>0.3874267869437278</v>
       </c>
     </row>
     <row r="28">
@@ -4092,7 +4092,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7315266803331284</v>
+        <v>0.3925601668999998</v>
       </c>
     </row>
     <row r="29">
@@ -4100,7 +4100,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>0.6324362647882658</v>
+        <v>0.3925601668999991</v>
       </c>
     </row>
     <row r="30">
@@ -4108,7 +4108,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5862784234552012</v>
+        <v>0.3925601668999955</v>
       </c>
     </row>
     <row r="31">
@@ -4116,7 +4116,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3763281536602175</v>
+        <v>0.3925601668999766</v>
       </c>
     </row>
     <row r="32">
@@ -4124,7 +4124,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3796352427385145</v>
+        <v>0.3925601668998784</v>
       </c>
     </row>
     <row r="33">
@@ -4132,7 +4132,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3514905684279914</v>
+        <v>0.392560166899369</v>
       </c>
     </row>
     <row r="34">
@@ -4140,7 +4140,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>0.3436730814091082</v>
+        <v>0.3925601668967239</v>
       </c>
     </row>
     <row r="35">
@@ -4148,7 +4148,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3348289715075891</v>
+        <v>0.3925601668829917</v>
       </c>
     </row>
     <row r="36">
@@ -4156,7 +4156,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3331893234998242</v>
+        <v>0.3925601668116988</v>
       </c>
     </row>
     <row r="37">
@@ -4164,7 +4164,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>0.333947974545635</v>
+        <v>0.3925601664415675</v>
       </c>
     </row>
     <row r="38">
@@ -4172,7 +4172,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>0.3344172645781615</v>
+        <v>0.3925601645199622</v>
       </c>
     </row>
     <row r="39">
@@ -4180,7 +4180,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>0.3350769404617849</v>
+        <v>0.3925601545435873</v>
       </c>
     </row>
     <row r="40">
@@ -4188,7 +4188,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>0.3353766193246073</v>
+        <v>0.3925601027493684</v>
       </c>
     </row>
     <row r="41">
@@ -4196,7 +4196,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>0.3353746917663612</v>
+        <v>0.3925598338500667</v>
       </c>
     </row>
     <row r="42">
@@ -4204,7 +4204,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>0.3355154467042921</v>
+        <v>0.3925584378117362</v>
       </c>
     </row>
     <row r="43">
@@ -4212,7 +4212,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3357487890335164</v>
+        <v>0.3925511900938659</v>
       </c>
     </row>
     <row r="44">
@@ -4220,7 +4220,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>0.3433100674593284</v>
+        <v>0.3925135642851064</v>
       </c>
     </row>
     <row r="45">
@@ -4228,7 +4228,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3344592131218199</v>
+        <v>0.3923182788524134</v>
       </c>
     </row>
     <row r="46">
@@ -4236,7 +4236,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3230732241042686</v>
+        <v>0.3913059253723687</v>
       </c>
     </row>
     <row r="47">
@@ -4244,7 +4244,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>0.3198989150893806</v>
+        <v>0.3860904133926276</v>
       </c>
     </row>
     <row r="48">
@@ -4252,7 +4252,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3302405053998392</v>
+        <v>0.3600564651505179</v>
       </c>
     </row>
     <row r="49">
@@ -4260,7 +4260,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>0.4050345750712405</v>
+        <v>0.2480510833501829</v>
       </c>
     </row>
     <row r="50">
@@ -4268,7 +4268,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>0.2784337529939935</v>
+        <v>-0.03719290026168892</v>
       </c>
     </row>
     <row r="51">
@@ -4276,7 +4276,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>0.7572079601207087</v>
+        <v>-0.3008142716812418</v>
       </c>
     </row>
     <row r="52">
@@ -4284,7 +4284,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>0.9956878531071215</v>
+        <v>-0.3937170648816554</v>
       </c>
     </row>
     <row r="53">
@@ -4292,7 +4292,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>1.126121971149564</v>
+        <v>-0.4145467869437278</v>
       </c>
     </row>
   </sheetData>
